--- a/Result/profitability/3217.xlsx
+++ b/Result/profitability/3217.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>2.77875</v>
+        <v>2.64</v>
       </c>
       <c r="N2" t="n">
-        <v>45.5025</v>
+        <v>44.90875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>2.40625</v>
+        <v>2.32</v>
       </c>
       <c r="N3" t="n">
-        <v>40.58875</v>
+        <v>40.20375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.10375</v>
+        <v>2.03125</v>
       </c>
       <c r="N4" t="n">
-        <v>36.075</v>
+        <v>35.735</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1875</v>
+        <v>1.1975</v>
       </c>
       <c r="N5" t="n">
-        <v>31.31875</v>
+        <v>31.24125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9762500000000002</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>27.825</v>
+        <v>27.37375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5437500000000001</v>
+        <v>0.43875</v>
       </c>
       <c r="N7" t="n">
-        <v>24.555</v>
+        <v>24.2525</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.23375</v>
+        <v>0.17875</v>
       </c>
       <c r="N8" t="n">
-        <v>21.21125</v>
+        <v>21.03625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>947</v>
+      </c>
+      <c r="D75" t="n">
+        <v>497</v>
+      </c>
+      <c r="E75" t="n">
+        <v>450</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>266</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>28.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>271</v>
+      </c>
+      <c r="K75" t="n">
+        <v>214</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.05625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.855</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1560283687943262</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.399999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02861230329041486</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.0347826086956522</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6199999999999974</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01287642782969878</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
